--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_18_R2.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_18_R2.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.4429</v>
+        <v>8.044600000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>9.707700000000001</v>
+        <v>8.4102</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2647</v>
+        <v>-0.3655</v>
       </c>
       <c r="G2" t="n">
         <v>1.3135</v>
@@ -610,13 +610,13 @@
         <v>3.4793</v>
       </c>
       <c r="S2" t="n">
-        <v>2.2918</v>
+        <v>0.8935</v>
       </c>
       <c r="T2" t="n">
-        <v>3.2912</v>
+        <v>1.9937</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.9994</v>
+        <v>-1.1002</v>
       </c>
       <c r="V2" t="n">
         <v>2.8223</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.0232</v>
+        <v>3.1919</v>
       </c>
       <c r="E3" t="n">
-        <v>6.4568</v>
+        <v>6.6927</v>
       </c>
       <c r="F3" t="n">
-        <v>-3.4336</v>
+        <v>-3.5008</v>
       </c>
       <c r="G3" t="n">
         <v>-0.3988</v>
@@ -688,13 +688,13 @@
         <v>2.3195</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4182</v>
+        <v>-0.2495</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8496</v>
+        <v>1.0855</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.2678</v>
+        <v>-1.335</v>
       </c>
       <c r="V3" t="n">
         <v>2.6805</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>K. MITOGLOU</t>
+          <t>C. OSMAN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2122</v>
+        <v>0.4157</v>
       </c>
       <c r="E4" t="n">
-        <v>3.8396</v>
+        <v>0.9157</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.6274</v>
+        <v>-0.5</v>
       </c>
       <c r="G4" t="n">
-        <v>-3.4133</v>
+        <v>-0.4012</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.1117</v>
+        <v>0.4753</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.3016</v>
+        <v>-0.8764999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.6757</v>
+        <v>0.4671</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.5321</v>
+        <v>0.3935</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8564000000000001</v>
+        <v>0.0736</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.7377</v>
+        <v>-0.8683</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5796</v>
+        <v>0.0818</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.1581</v>
+        <v>-0.9500999999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>2.0876</v>
+        <v>0.9278</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.0876</v>
+        <v>0.9278</v>
       </c>
       <c r="S4" t="n">
-        <v>3.6102</v>
+        <v>-0.2526</v>
       </c>
       <c r="T4" t="n">
-        <v>3.9792</v>
+        <v>0.3068</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.369</v>
+        <v>-0.5594</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.0722</v>
+        <v>0.1418</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5361</v>
+        <v>0.1418</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.6083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0677</v>
+        <v>0.0848</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.3124</v>
+        <v>-1.1944</v>
       </c>
       <c r="F5" t="n">
-        <v>1.3801</v>
+        <v>1.2793</v>
       </c>
       <c r="G5" t="n">
         <v>-0.8597</v>
@@ -844,13 +844,13 @@
         <v>1.1598</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2315</v>
+        <v>0.2486</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1494</v>
+        <v>-0.0314</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3809</v>
+        <v>0.2801</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C. OSMAN</t>
+          <t>O. YURTSEVEN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.4093</v>
+        <v>-0.6362</v>
       </c>
       <c r="E6" t="n">
-        <v>0.326</v>
+        <v>-0.291</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.7352</v>
+        <v>-0.3452</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.4012</v>
+        <v>0.4194</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4753</v>
+        <v>0.9915</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8764999999999999</v>
+        <v>-0.572</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4671</v>
+        <v>1.4662</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3935</v>
+        <v>0.8773</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0736</v>
+        <v>0.5889</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8683</v>
+        <v>-1.0468</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0818</v>
+        <v>0.1141</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.9500999999999999</v>
+        <v>-1.1609</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9278</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q6" t="n">
+        <v>-1.6237</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.1598</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-0.5917</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-0.1336</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-0.4582</v>
+      </c>
+      <c r="V6" t="n">
         <v>0</v>
       </c>
-      <c r="R6" t="n">
-        <v>0.9278</v>
-      </c>
-      <c r="S6" t="n">
-        <v>-1.0776</v>
-      </c>
-      <c r="T6" t="n">
-        <v>-0.2829</v>
-      </c>
-      <c r="U6" t="n">
-        <v>-0.7947</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0.1418</v>
-      </c>
       <c r="W6" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>O. YURTSEVEN</t>
+          <t>K. MITOGLOU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.7034</v>
+        <v>-1.3992</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.291</v>
+        <v>1.3626</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4124</v>
+        <v>-2.7618</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4194</v>
+        <v>-3.4133</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9915</v>
+        <v>-2.1117</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.572</v>
+        <v>-1.3016</v>
       </c>
       <c r="J7" t="n">
-        <v>1.4662</v>
+        <v>-0.6757</v>
       </c>
       <c r="K7" t="n">
-        <v>0.8773</v>
+        <v>-1.5321</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5889</v>
+        <v>0.8564000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.0468</v>
+        <v>-2.7377</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1141</v>
+        <v>-0.5796</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.1609</v>
+        <v>-2.1581</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.4639</v>
+        <v>2.0876</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.6237</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1598</v>
+        <v>2.0876</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6589</v>
+        <v>0.9987</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1336</v>
+        <v>1.5022</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5254</v>
+        <v>-0.5034</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.1701</v>
+        <v>-1.6647</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.3033</v>
+        <v>-1.8315</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1332</v>
+        <v>0.1668</v>
       </c>
       <c r="G8" t="n">
         <v>-0.8496</v>
@@ -1078,13 +1078,13 @@
         <v>1.1598</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3747</v>
+        <v>0.1307</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1415</v>
+        <v>0.3304</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2333</v>
+        <v>-0.1997</v>
       </c>
       <c r="V8" t="n">
         <v>0.6778999999999999</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. HOLMES</t>
+          <t>J. GRANT</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.8702</v>
+        <v>-2.8283</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.12</v>
+        <v>-1.1744</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.7502</v>
+        <v>-1.654</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.3</v>
+        <v>-2.1672</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.6878</v>
+        <v>-1.2905</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6122</v>
+        <v>-0.8767</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.3814</v>
+        <v>-0.4478</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.4551</v>
+        <v>-0.6785</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0736</v>
+        <v>0.2308</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.9186</v>
+        <v>-1.7194</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2327</v>
+        <v>-0.612</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6859</v>
+        <v>-1.1074</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.4639</v>
+        <v>-1.6237</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1598</v>
+        <v>-3.4793</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6959</v>
+        <v>1.8556</v>
       </c>
       <c r="S9" t="n">
-        <v>0.8241000000000001</v>
+        <v>0.3156</v>
       </c>
       <c r="T9" t="n">
-        <v>1.2072</v>
+        <v>1.1444</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3831</v>
+        <v>-0.8287</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.9304</v>
+        <v>0.6468</v>
       </c>
       <c r="W9" t="n">
-        <v>1.214</v>
+        <v>1.6083</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.1444</v>
+        <v>-0.9615</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>N. ROGKAVOPOULOS</t>
+          <t>R. HOLMES</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.6683</v>
+        <v>-3.1733</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.4733</v>
+        <v>-0.3559</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.1951</v>
+        <v>-2.8174</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.7197</v>
+        <v>-2.3</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.1199</v>
+        <v>-1.6878</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.5998</v>
+        <v>-0.6122</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.1078</v>
+        <v>-1.3814</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.7191</v>
+        <v>-1.4551</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.3887</v>
+        <v>0.0736</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.612</v>
+        <v>-0.9186</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4008</v>
+        <v>-0.2327</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.2112</v>
+        <v>-0.6859</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9278</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9278</v>
+        <v>0.6959</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8764</v>
+        <v>0.521</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3655</v>
+        <v>0.9713000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5109</v>
+        <v>-0.4503</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-0.9304</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.214</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>K. NUNN</t>
+          <t>N. ROGKAVOPOULOS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.4158</v>
+        <v>-3.1959</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.8672</v>
+        <v>-1.7656</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.5487</v>
+        <v>-1.4303</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.4348</v>
+        <v>-3.7197</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.1119</v>
+        <v>-1.1199</v>
       </c>
       <c r="I11" t="n">
-        <v>-4.3229</v>
+        <v>-2.5998</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.2939</v>
+        <v>-2.1078</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1316</v>
+        <v>-0.7191</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.4255</v>
+        <v>-1.3887</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.1409</v>
+        <v>-1.612</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2435</v>
+        <v>-0.4008</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.8974</v>
+        <v>-1.2112</v>
       </c>
       <c r="P11" t="n">
-        <v>-0</v>
+        <v>0.9278</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.7834</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.7834</v>
+        <v>0.9278</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7697000000000001</v>
+        <v>-0.4039</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1379</v>
+        <v>0.3422</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.9076</v>
+        <v>-0.7461</v>
       </c>
       <c r="V11" t="n">
-        <v>0.7886</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.2836</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. GRANT</t>
+          <t>K. NUNN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.6477</v>
+        <v>-3.9783</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.8257</v>
+        <v>-2.6313</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.822</v>
+        <v>-1.347</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.1672</v>
+        <v>-4.4348</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.2905</v>
+        <v>-0.1119</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.8767</v>
+        <v>-4.3229</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.4478</v>
+        <v>-1.2939</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.6785</v>
+        <v>0.1316</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2308</v>
+        <v>-1.4255</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.7194</v>
+        <v>-3.1409</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.612</v>
+        <v>-0.2435</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.1074</v>
+        <v>-2.8974</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.6237</v>
+        <v>-0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.4793</v>
+        <v>-2.7834</v>
       </c>
       <c r="R12" t="n">
-        <v>1.8556</v>
+        <v>2.7834</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.5037</v>
+        <v>-0.3321</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.507</v>
+        <v>0.3738</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.9968</v>
+        <v>-0.7059</v>
       </c>
       <c r="V12" t="n">
-        <v>0.6468</v>
+        <v>0.7886</v>
       </c>
       <c r="W12" t="n">
-        <v>1.6083</v>
+        <v>1.0722</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.9615</v>
+        <v>-0.2836</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.1388</v>
+        <v>-5.138899999999998</v>
       </c>
       <c r="E13" t="n">
-        <v>8.1372</v>
+        <v>8.1371</v>
       </c>
       <c r="F13" t="n">
-        <v>-13.276</v>
+        <v>-13.2759</v>
       </c>
       <c r="G13" t="n">
         <v>-16.8114</v>
@@ -1447,7 +1447,7 @@
         <v>-2.6919</v>
       </c>
       <c r="L13" t="n">
-        <v>4.499500000000001</v>
+        <v>4.499499999999999</v>
       </c>
       <c r="M13" t="n">
         <v>-18.6191</v>
@@ -1468,22 +1468,22 @@
         <v>18.5563</v>
       </c>
       <c r="S13" t="n">
-        <v>1.2784</v>
+        <v>1.2783</v>
       </c>
       <c r="T13" t="n">
-        <v>7.885199999999999</v>
+        <v>7.885300000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-6.607100000000001</v>
+        <v>-6.606800000000001</v>
       </c>
       <c r="V13" t="n">
-        <v>5.755299999999999</v>
+        <v>5.7553</v>
       </c>
       <c r="W13" t="n">
         <v>12.3614</v>
       </c>
       <c r="X13" t="n">
-        <v>-6.606100000000001</v>
+        <v>-6.6061</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.219</v>
+        <v>5.9774</v>
       </c>
       <c r="E14" t="n">
-        <v>5.9588</v>
+        <v>5.3691</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2602</v>
+        <v>0.6083</v>
       </c>
       <c r="G14" t="n">
         <v>6.1453</v>
@@ -1546,13 +1546,13 @@
         <v>1.8556</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3958</v>
+        <v>0.1542</v>
       </c>
       <c r="T14" t="n">
-        <v>1.7695</v>
+        <v>1.1797</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.3737</v>
+        <v>-1.0255</v>
       </c>
       <c r="V14" t="n">
         <v>0.1418</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>W. HERNANGOMEZ</t>
+          <t>N. LAPROVITTOLA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.0631</v>
+        <v>5.0839</v>
       </c>
       <c r="E15" t="n">
-        <v>2.985</v>
+        <v>4.9419</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0781</v>
+        <v>0.1419</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2114</v>
+        <v>6.0279</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.9363</v>
+        <v>1.5679</v>
       </c>
       <c r="I15" t="n">
-        <v>1.1477</v>
+        <v>4.4599</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.1066</v>
+        <v>6.6858</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.4684</v>
+        <v>1.6973</v>
       </c>
       <c r="L15" t="n">
-        <v>1.3618</v>
+        <v>4.9885</v>
       </c>
       <c r="M15" t="n">
-        <v>0.318</v>
+        <v>-0.658</v>
       </c>
       <c r="N15" t="n">
-        <v>0.5321</v>
+        <v>-0.1294</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.214</v>
+        <v>-0.5286</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.6959</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.3195</v>
+        <v>-2.7834</v>
       </c>
       <c r="R15" t="n">
-        <v>1.6237</v>
+        <v>1.8556</v>
       </c>
       <c r="S15" t="n">
-        <v>1.1892</v>
+        <v>0.5199</v>
       </c>
       <c r="T15" t="n">
-        <v>1.9109</v>
+        <v>0.5034</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.7218</v>
+        <v>0.0165</v>
       </c>
       <c r="V15" t="n">
-        <v>3.3584</v>
+        <v>-0.5361</v>
       </c>
       <c r="W15" t="n">
-        <v>3.5002</v>
+        <v>0.5361</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1418</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>N. LAPROVITTOLA</t>
+          <t>T. SHENGELIA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.7921</v>
+        <v>3.1537</v>
       </c>
       <c r="E16" t="n">
-        <v>3.9983</v>
+        <v>3.3055</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.2062</v>
+        <v>-0.1518</v>
       </c>
       <c r="G16" t="n">
-        <v>6.0279</v>
+        <v>4.3137</v>
       </c>
       <c r="H16" t="n">
-        <v>1.5679</v>
+        <v>3.4203</v>
       </c>
       <c r="I16" t="n">
-        <v>4.4599</v>
+        <v>0.8934</v>
       </c>
       <c r="J16" t="n">
-        <v>6.6858</v>
+        <v>3.474</v>
       </c>
       <c r="K16" t="n">
-        <v>1.6973</v>
+        <v>2.4703</v>
       </c>
       <c r="L16" t="n">
-        <v>4.9885</v>
+        <v>1.0037</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.658</v>
+        <v>0.8397</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1294</v>
+        <v>0.95</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.5286</v>
+        <v>-0.1103</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.9278</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.7834</v>
+        <v>-2.3195</v>
       </c>
       <c r="R16" t="n">
         <v>1.8556</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.7718</v>
+        <v>-0.6961000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4402</v>
+        <v>0.5427</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3317</v>
+        <v>-1.2388</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5361</v>
+        <v>1.6083</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.0722</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>T. SHENGELIA</t>
+          <t>W. HERNANGOMEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.4853</v>
+        <v>3.1481</v>
       </c>
       <c r="E17" t="n">
-        <v>2.9517</v>
+        <v>1.9235</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4664</v>
+        <v>1.2246</v>
       </c>
       <c r="G17" t="n">
-        <v>4.3137</v>
+        <v>0.2114</v>
       </c>
       <c r="H17" t="n">
-        <v>3.4203</v>
+        <v>-0.9363</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8934</v>
+        <v>1.1477</v>
       </c>
       <c r="J17" t="n">
-        <v>3.474</v>
+        <v>-0.1066</v>
       </c>
       <c r="K17" t="n">
-        <v>2.4703</v>
+        <v>-1.4684</v>
       </c>
       <c r="L17" t="n">
-        <v>1.0037</v>
+        <v>1.3618</v>
       </c>
       <c r="M17" t="n">
-        <v>0.8397</v>
+        <v>0.318</v>
       </c>
       <c r="N17" t="n">
-        <v>0.95</v>
+        <v>0.5321</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1103</v>
+        <v>-0.214</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.4639</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q17" t="n">
         <v>-2.3195</v>
       </c>
       <c r="R17" t="n">
-        <v>1.8556</v>
+        <v>1.6237</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.3645</v>
+        <v>0.2741</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1889</v>
+        <v>0.8494</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.5534</v>
+        <v>-0.5753</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>3.3584</v>
       </c>
       <c r="W17" t="n">
-        <v>1.6083</v>
+        <v>3.5002</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.6083</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8375</v>
+        <v>2.6512</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1346</v>
+        <v>1.4321</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7029</v>
+        <v>1.2191</v>
       </c>
       <c r="G18" t="n">
         <v>1.5414</v>
@@ -1858,13 +1858,13 @@
         <v>1.8556</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.7607</v>
+        <v>0.0529</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5975</v>
+        <v>0.7</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.1633</v>
+        <v>-0.6471</v>
       </c>
       <c r="V18" t="n">
         <v>2.6805</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.0374</v>
+        <v>-1.1103</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.5384</v>
+        <v>-0.8922</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.499</v>
+        <v>-0.2181</v>
       </c>
       <c r="G19" t="n">
         <v>0.0699</v>
@@ -1936,13 +1936,13 @@
         <v>1.1598</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6814</v>
+        <v>0.6084000000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>1.0578</v>
+        <v>0.704</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3765</v>
+        <v>-0.0955</v>
       </c>
       <c r="V19" t="n">
         <v>-1.3247</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.4113</v>
+        <v>-1.1189</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.9088000000000001</v>
+        <v>-0.6729000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.5024999999999999</v>
+        <v>-0.446</v>
       </c>
       <c r="G20" t="n">
         <v>-0.264</v>
@@ -2014,13 +2014,13 @@
         <v>0.4639</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3071</v>
+        <v>-0.0147</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2987</v>
+        <v>-0.06279999999999999</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0083</v>
+        <v>0.0481</v>
       </c>
       <c r="V20" t="n">
         <v>-1.0722</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.6811</v>
+        <v>-1.7204</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7048</v>
+        <v>0.351</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.3859</v>
+        <v>-2.0713</v>
       </c>
       <c r="G21" t="n">
         <v>1.175</v>
@@ -2092,13 +2092,13 @@
         <v>0.9278</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4797</v>
+        <v>-0.519</v>
       </c>
       <c r="T21" t="n">
-        <v>0.9752</v>
+        <v>0.6214</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.455</v>
+        <v>-1.1404</v>
       </c>
       <c r="V21" t="n">
         <v>-2.1444</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.363</v>
+        <v>-1.9641</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.1336</v>
+        <v>-1.0157</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.2293</v>
+        <v>-0.9484</v>
       </c>
       <c r="G22" t="n">
         <v>-1.5341</v>
@@ -2170,13 +2170,13 @@
         <v>0.9278</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4573</v>
+        <v>0.8562</v>
       </c>
       <c r="T22" t="n">
-        <v>0.4208</v>
+        <v>0.5387999999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0365</v>
+        <v>0.3174</v>
       </c>
       <c r="V22" t="n">
         <v>-1.7501</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.4759</v>
+        <v>-2.7175</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.1976</v>
+        <v>-0.7873</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.2783</v>
+        <v>-1.9301</v>
       </c>
       <c r="G23" t="n">
         <v>0.1509</v>
@@ -2248,13 +2248,13 @@
         <v>0.9278</v>
       </c>
       <c r="S23" t="n">
-        <v>0.8913</v>
+        <v>0.6497000000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>1.1246</v>
+        <v>0.5348000000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2333</v>
+        <v>0.1149</v>
       </c>
       <c r="V23" t="n">
         <v>-2.8223</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.2897</v>
+        <v>-3.0988</v>
       </c>
       <c r="E24" t="n">
         <v>0.5351</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.8248</v>
+        <v>-3.6339</v>
       </c>
       <c r="G24" t="n">
         <v>-1.0259</v>
@@ -2326,13 +2326,13 @@
         <v>0.4639</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2095</v>
+        <v>-0.0187</v>
       </c>
       <c r="T24" t="n">
         <v>0.4955</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.7050999999999999</v>
+        <v>-0.5142</v>
       </c>
       <c r="V24" t="n">
         <v>-2.2862</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>5.1386</v>
+        <v>8.284299999999998</v>
       </c>
       <c r="E25" t="n">
-        <v>14.4899</v>
+        <v>14.4901</v>
       </c>
       <c r="F25" t="n">
-        <v>-9.3512</v>
+        <v>-6.2057</v>
       </c>
       <c r="G25" t="n">
         <v>16.8115</v>
@@ -2380,7 +2380,7 @@
         <v>18.619</v>
       </c>
       <c r="K25" t="n">
-        <v>3.329200000000001</v>
+        <v>3.3292</v>
       </c>
       <c r="L25" t="n">
         <v>15.2897</v>
@@ -2392,7 +2392,7 @@
         <v>2.692</v>
       </c>
       <c r="O25" t="n">
-        <v>-4.499499999999999</v>
+        <v>-4.4995</v>
       </c>
       <c r="P25" t="n">
         <v>-4.6391</v>
@@ -2404,13 +2404,13 @@
         <v>13.9171</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.2783</v>
+        <v>1.8669</v>
       </c>
       <c r="T25" t="n">
-        <v>6.6068</v>
+        <v>6.6069</v>
       </c>
       <c r="U25" t="n">
-        <v>-7.885599999999999</v>
+        <v>-4.7399</v>
       </c>
       <c r="V25" t="n">
         <v>-5.7553</v>
